--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -167,7 +167,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -177,12 +177,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9EAF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBDD7EE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -233,17 +227,17 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,70 +46,34 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
-    <t>Час</t>
-  </si>
-  <si>
     <t>Километри</t>
   </si>
   <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
-  </si>
-  <si>
-    <t>1199 Varna Car Osvoboditel</t>
-  </si>
-  <si>
-    <t>1146 Варна Сливница</t>
-  </si>
-  <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Сливница</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
+  </si>
+  <si>
+    <t>В7225ВР</t>
   </si>
   <si>
     <t>В6513КС</t>
   </si>
   <si>
-    <t>В7225ВР</t>
+    <t>78970155027720246</t>
   </si>
   <si>
     <t>78970155027720238</t>
   </si>
   <si>
-    <t>78970155027720246</t>
+    <t>E GAS LPG</t>
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>12:54:00</t>
-  </si>
-  <si>
-    <t>14:03:00</t>
-  </si>
-  <si>
-    <t>14:38:00</t>
-  </si>
-  <si>
-    <t>11:12:00</t>
-  </si>
-  <si>
-    <t>3232057198 3232057198</t>
-  </si>
-  <si>
-    <t>3232203353 3232203353</t>
-  </si>
-  <si>
-    <t>3232518069 3232518069</t>
-  </si>
-  <si>
-    <t>3232529561 3232529561</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -532,7 +493,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N12"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -541,17 +502,14 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -585,283 +543,203 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46181</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="H2">
+        <v>14.2</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.72</v>
+      </c>
+      <c r="J2">
+        <v>14.4</v>
+      </c>
+      <c r="K2">
+        <v>42470</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="3">
+        <v>46182</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
+        <v>20</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H3">
+        <v>30.6</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J3">
+        <v>31.2</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="3">
+        <v>46183</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46160</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="C4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="H4">
+        <v>15.3</v>
+      </c>
+      <c r="I4" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="J4">
+        <v>15.6</v>
+      </c>
+      <c r="K4">
+        <v>42540</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="7">
+        <v>30</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.53</v>
+      </c>
+      <c r="E9" s="7">
+        <v>45.9</v>
+      </c>
+      <c r="F9" s="7">
+        <v>46.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B10" s="7">
         <v>20</v>
       </c>
-      <c r="E2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F2">
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.71</v>
+      </c>
+      <c r="E10" s="7">
+        <v>14.2</v>
+      </c>
+      <c r="F10" s="7">
+        <v>14.4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2">
-        <v>1.52</v>
-      </c>
-      <c r="I2" s="1">
-        <v>38</v>
-      </c>
-      <c r="J2">
-        <v>1.55</v>
-      </c>
-      <c r="K2" s="1">
-        <v>38.75</v>
-      </c>
-      <c r="L2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46163</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>21</v>
-      </c>
-      <c r="E3" t="s">
-        <v>22</v>
-      </c>
-      <c r="F3">
-        <v>9.99</v>
-      </c>
-      <c r="G3" t="s">
-        <v>24</v>
-      </c>
-      <c r="H3">
-        <v>1.54</v>
-      </c>
-      <c r="I3" s="1">
-        <v>15.38</v>
-      </c>
-      <c r="J3">
-        <v>1.57</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15.68</v>
-      </c>
-      <c r="L3" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3">
-        <v>42170</v>
-      </c>
-      <c r="N3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4">
-        <v>25</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4">
-        <v>1.54</v>
-      </c>
-      <c r="I4" s="1">
-        <v>38.5</v>
-      </c>
-      <c r="J4">
-        <v>1.57</v>
-      </c>
-      <c r="K4" s="1">
-        <v>39.25</v>
-      </c>
-      <c r="L4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="3">
-        <v>46170</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5">
-        <v>20</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5">
-        <v>0.76</v>
-      </c>
-      <c r="I5" s="1">
-        <v>15.2</v>
-      </c>
-      <c r="J5">
-        <v>0.77</v>
-      </c>
-      <c r="K5" s="1">
-        <v>15.4</v>
-      </c>
-      <c r="L5" t="s">
-        <v>28</v>
-      </c>
-      <c r="M5">
-        <v>42290</v>
-      </c>
-      <c r="N5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="7">
-        <v>59.99</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B11" s="10">
+        <v>50</v>
+      </c>
+      <c r="C11" s="10">
         <v>3</v>
       </c>
-      <c r="D10" s="8">
-        <v>1.5316</v>
-      </c>
-      <c r="E10" s="7">
-        <v>91.88</v>
-      </c>
-      <c r="F10" s="7">
-        <v>93.68000000000001</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="7">
-        <v>20</v>
-      </c>
-      <c r="C11" s="7">
-        <v>1</v>
-      </c>
-      <c r="D11" s="8">
-        <v>0.76</v>
-      </c>
-      <c r="E11" s="7">
-        <v>15.2</v>
-      </c>
-      <c r="F11" s="7">
-        <v>15.4</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="9" t="s">
-        <v>38</v>
-      </c>
-      <c r="B12" s="10">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>107.08</v>
-      </c>
-      <c r="F12" s="10">
-        <v>109.08</v>
+      <c r="D11" s="8"/>
+      <c r="E11" s="10">
+        <v>60.1</v>
+      </c>
+      <c r="F11" s="10">
+        <v>61.2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -46,9 +46,15 @@
     <t>Сума по ЕКО цена</t>
   </si>
   <si>
+    <t>Час</t>
+  </si>
+  <si>
     <t>Километри</t>
   </si>
   <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
     <t>Варна Порт</t>
   </si>
   <si>
@@ -74,6 +80,15 @@
   </si>
   <si>
     <t>95 EKONOMY UNLEADED</t>
+  </si>
+  <si>
+    <t>10:12</t>
+  </si>
+  <si>
+    <t>12:21</t>
+  </si>
+  <si>
+    <t>12:06</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -493,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -506,10 +521,12 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -543,22 +560,28 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46181</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>20</v>
@@ -575,25 +598,31 @@
       <c r="J2">
         <v>14.4</v>
       </c>
-      <c r="K2">
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
         <v>42470</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>216247</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" s="3">
         <v>46182</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -610,25 +639,31 @@
       <c r="J3">
         <v>31.2</v>
       </c>
-      <c r="K3">
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>140219</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" s="3">
         <v>46183</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C4" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -645,13 +680,19 @@
       <c r="J4">
         <v>15.6</v>
       </c>
-      <c r="K4">
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
         <v>42540</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M4">
+        <v>110677</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" s="4" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4"/>
       <c r="C7" s="4"/>
@@ -659,18 +700,18 @@
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:13">
       <c r="A8" s="5" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E8" s="5" t="s">
         <v>7</v>
@@ -679,9 +720,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:13">
       <c r="A9" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B9" s="7">
         <v>30</v>
@@ -699,9 +740,9 @@
         <v>46.8</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:13">
       <c r="A10" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B10" s="7">
         <v>20</v>
@@ -719,9 +760,9 @@
         <v>14.4</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:13">
       <c r="A11" s="9" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B11" s="10">
         <v>50</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
   <si>
     <t>Дата</t>
   </si>
@@ -49,46 +49,19 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Километри</t>
-  </si>
-  <si>
-    <t>Billing_Document</t>
-  </si>
-  <si>
     <t>Варна Порт</t>
   </si>
   <si>
-    <t>Варна Сливница</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
     <t>В7225ВР</t>
   </si>
   <si>
-    <t>В6513КС</t>
-  </si>
-  <si>
     <t>78970155027720246</t>
   </si>
   <si>
-    <t>78970155027720238</t>
-  </si>
-  <si>
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>95 EKONOMY UNLEADED</t>
-  </si>
-  <si>
-    <t>10:12</t>
-  </si>
-  <si>
-    <t>12:21</t>
-  </si>
-  <si>
-    <t>12:06</t>
+    <t>2026-06-16 14:34:54</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -508,7 +481,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:K8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,12 +494,10 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="21.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:11">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -560,227 +531,113 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="3">
+        <v>46189</v>
+      </c>
+      <c r="B2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="C2" t="s">
         <v>12</v>
       </c>
+      <c r="D2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2">
+        <v>30.39</v>
+      </c>
+      <c r="G2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H2">
+        <v>20.06</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J2">
+        <v>20.36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="3">
-        <v>46181</v>
-      </c>
-      <c r="B2" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" t="s">
+    <row r="5" spans="1:11">
+      <c r="A5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="4"/>
+      <c r="F5" s="4"/>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="C6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="H2">
-        <v>14.2</v>
-      </c>
-      <c r="I2" s="1">
-        <v>0.72</v>
-      </c>
-      <c r="J2">
-        <v>14.4</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2">
-        <v>42470</v>
-      </c>
-      <c r="M2">
-        <v>216247</v>
+      <c r="E6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46182</v>
-      </c>
-      <c r="B3" t="s">
+    <row r="7" spans="1:11">
+      <c r="A7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
+      <c r="B7" s="7">
+        <v>30.39</v>
+      </c>
+      <c r="C7" s="7">
+        <v>1</v>
+      </c>
+      <c r="D7" s="8">
+        <v>0.6601</v>
+      </c>
+      <c r="E7" s="7">
+        <v>20.06</v>
+      </c>
+      <c r="F7" s="7">
+        <v>20.36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="F3">
-        <v>20</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H3">
-        <v>30.6</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J3">
-        <v>31.2</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>140219</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46183</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>10</v>
-      </c>
-      <c r="G4" s="1">
-        <v>1.53</v>
-      </c>
-      <c r="H4">
-        <v>15.3</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="J4">
-        <v>15.6</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
-        <v>42540</v>
-      </c>
-      <c r="M4">
-        <v>110677</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="7">
-        <v>30</v>
-      </c>
-      <c r="C9" s="7">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8">
-        <v>1.53</v>
-      </c>
-      <c r="E9" s="7">
-        <v>45.9</v>
-      </c>
-      <c r="F9" s="7">
-        <v>46.8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="7">
-        <v>20</v>
-      </c>
-      <c r="C10" s="7">
+      <c r="B8" s="10">
+        <v>30.39</v>
+      </c>
+      <c r="C8" s="10">
         <v>1</v>
       </c>
-      <c r="D10" s="8">
-        <v>0.71</v>
-      </c>
-      <c r="E10" s="7">
-        <v>14.2</v>
-      </c>
-      <c r="F10" s="7">
-        <v>14.4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="10">
-        <v>50</v>
-      </c>
-      <c r="C11" s="10">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>60.1</v>
-      </c>
-      <c r="F11" s="10">
-        <v>61.2</v>
+      <c r="D8" s="8"/>
+      <c r="E8" s="10">
+        <v>20.06</v>
+      </c>
+      <c r="F8" s="10">
+        <v>20.36</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A5:F5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -49,7 +52,13 @@
     <t>Час</t>
   </si>
   <si>
-    <t>Варна Порт</t>
+    <t>Километри</t>
+  </si>
+  <si>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В7225ВР</t>
@@ -61,7 +70,13 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>2026-06-16 14:34:54</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>14:35:00</t>
+  </si>
+  <si>
+    <t>3233441809 3233441809</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -481,7 +496,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -490,14 +505,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -531,45 +549,63 @@
       <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
+      <c r="L1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2">
         <v>30.39</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2">
         <v>0.66</v>
       </c>
-      <c r="H2">
+      <c r="I2" s="1">
         <v>20.06</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>0.67</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>20.36</v>
       </c>
-      <c r="K2" t="s">
-        <v>15</v>
+      <c r="L2" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2">
+        <v>42700</v>
+      </c>
+      <c r="N2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:14">
       <c r="A5" s="4" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -577,29 +613,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:14">
       <c r="A6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="6" t="s">
         <v>17</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="B7" s="7">
         <v>30.39</v>
@@ -617,9 +653,9 @@
         <v>20.36</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:14">
       <c r="A8" s="9" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B8" s="10">
         <v>30.39</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="24">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,7 +55,7 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
+    <t>Варна Порт</t>
   </si>
   <si>
     <t>В7225ВР</t>
@@ -70,13 +67,7 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>14:35:00</t>
-  </si>
-  <si>
-    <t>3233441809 3233441809</t>
+    <t>14:35</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -496,7 +487,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -505,17 +496,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -555,57 +545,51 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
-        <v>13</v>
-      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:13">
       <c r="A2" s="3">
         <v>46189</v>
       </c>
       <c r="B2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
       </c>
       <c r="F2">
         <v>30.39</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="H2">
+        <v>20.06</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="J2">
+        <v>20.36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>17</v>
+      </c>
+      <c r="L2">
+        <v>42700</v>
+      </c>
+      <c r="M2">
+        <v>219903</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="H2">
-        <v>0.66</v>
-      </c>
-      <c r="I2" s="1">
-        <v>20.06</v>
-      </c>
-      <c r="J2">
-        <v>0.67</v>
-      </c>
-      <c r="K2" s="1">
-        <v>20.36</v>
-      </c>
-      <c r="L2" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2">
-        <v>42700</v>
-      </c>
-      <c r="N2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="B5" s="4"/>
       <c r="C5" s="4"/>
@@ -613,29 +597,29 @@
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:13">
       <c r="A6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="E6" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:13">
       <c r="A7" s="6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B7" s="7">
         <v>30.39</v>
@@ -653,9 +637,9 @@
         <v>20.36</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:13">
       <c r="A8" s="9" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B8" s="10">
         <v>30.39</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -52,40 +55,37 @@
     <t>Километри</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна</t>
-  </si>
-  <si>
-    <t>В7225ВР</t>
+    <t>Billing_Document</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
+  </si>
+  <si>
+    <t>1158 Варна Чайка</t>
   </si>
   <si>
     <t>В6513КС</t>
   </si>
   <si>
-    <t>78970155027720246</t>
-  </si>
-  <si>
     <t>78970155027720238</t>
   </si>
   <si>
-    <t>E GAS LPG</t>
-  </si>
-  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>2026-07-01 10:38:43</t>
-  </si>
-  <si>
-    <t>2026-07-02 10:40:06</t>
-  </si>
-  <si>
-    <t>2026-07-02 11:00:01</t>
-  </si>
-  <si>
-    <t>2026-07-14 15:34:30</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:14:00</t>
+  </si>
+  <si>
+    <t>11:16:00</t>
+  </si>
+  <si>
+    <t>3234894482 3234894482</t>
+  </si>
+  <si>
+    <t>3235484095 3235484095</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -505,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -514,15 +514,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="21.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -559,250 +561,172 @@
       <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46204</v>
+        <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
       <c r="F2">
-        <v>31.2</v>
-      </c>
-      <c r="G2" s="1">
-        <v>0.65</v>
+        <v>25</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
       </c>
       <c r="H2">
-        <v>20.28</v>
+        <v>1.47</v>
       </c>
       <c r="I2" s="1">
-        <v>0.66</v>
+        <v>36.75</v>
       </c>
       <c r="J2">
-        <v>20.59</v>
-      </c>
-      <c r="K2" t="s">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="L2">
-        <v>42950</v>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
-        <v>46205</v>
+        <v>46231</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
         <v>19</v>
       </c>
-      <c r="F3">
-        <v>9.99</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.47</v>
-      </c>
       <c r="H3">
-        <v>14.69</v>
+        <v>1.53</v>
       </c>
       <c r="I3" s="1">
-        <v>1.5</v>
+        <v>15.3</v>
       </c>
       <c r="J3">
-        <v>14.98</v>
-      </c>
-      <c r="K3" t="s">
+        <v>1.56</v>
+      </c>
+      <c r="K3" s="1">
+        <v>15.6</v>
+      </c>
+      <c r="L3" t="s">
         <v>21</v>
       </c>
-      <c r="L3">
-        <v>42980</v>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
-      <c r="A4" s="3">
-        <v>46205</v>
-      </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F4">
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="H4">
-        <v>36.75</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="J4">
-        <v>37.5</v>
-      </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-      <c r="L4">
-        <v>0</v>
+      <c r="B7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:12">
-      <c r="A5" s="3">
-        <v>46217</v>
-      </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" t="s">
+    <row r="8" spans="1:14">
+      <c r="A8" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="F5">
-        <v>32.64</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0.62</v>
-      </c>
-      <c r="H5">
-        <v>20.24</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0.63</v>
-      </c>
-      <c r="J5">
-        <v>20.56</v>
-      </c>
-      <c r="K5" t="s">
-        <v>23</v>
-      </c>
-      <c r="L5">
-        <v>43300</v>
+      <c r="B8" s="7">
+        <v>35</v>
+      </c>
+      <c r="C8" s="7">
+        <v>2</v>
+      </c>
+      <c r="D8" s="8">
+        <v>1.4871</v>
+      </c>
+      <c r="E8" s="7">
+        <v>52.05</v>
+      </c>
+      <c r="F8" s="7">
+        <v>53.1</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
-      <c r="A8" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="4"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4"/>
-    </row>
-    <row r="9" spans="1:12">
-      <c r="A9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12">
-      <c r="A10" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B10" s="7">
-        <v>63.84</v>
-      </c>
-      <c r="C10" s="7">
+    <row r="9" spans="1:14">
+      <c r="A9" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="10">
+        <v>35</v>
+      </c>
+      <c r="C9" s="10">
         <v>2</v>
       </c>
-      <c r="D10" s="8">
-        <v>0.6347</v>
-      </c>
-      <c r="E10" s="7">
-        <v>40.52</v>
-      </c>
-      <c r="F10" s="7">
-        <v>41.15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="6" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="7">
-        <v>34.99</v>
-      </c>
-      <c r="C11" s="7">
-        <v>2</v>
-      </c>
-      <c r="D11" s="8">
-        <v>1.4701</v>
-      </c>
-      <c r="E11" s="7">
-        <v>51.44</v>
-      </c>
-      <c r="F11" s="7">
-        <v>52.48</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12">
-      <c r="A12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B12" s="10">
-        <v>98.83</v>
-      </c>
-      <c r="C12" s="10">
-        <v>4</v>
-      </c>
-      <c r="D12" s="8"/>
-      <c r="E12" s="10">
-        <v>91.95999999999999</v>
-      </c>
-      <c r="F12" s="10">
-        <v>93.63</v>
+      <c r="D9" s="8"/>
+      <c r="E9" s="10">
+        <v>52.05</v>
+      </c>
+      <c r="F9" s="10">
+        <v>53.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -113,7 +113,7 @@
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -697,7 +697,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>1.4871</v>
+        <v>1.487143</v>
       </c>
       <c r="E8" s="7">
         <v>52.05</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -505,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -518,13 +521,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -567,98 +570,107 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:15">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2">
         <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H2">
+        <v>1.369</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.47</v>
       </c>
-      <c r="I2" s="1">
+      <c r="J2">
         <v>36.75</v>
       </c>
-      <c r="J2">
+      <c r="K2" s="1">
         <v>1.5</v>
       </c>
-      <c r="K2" s="1">
+      <c r="L2" s="1">
         <v>37.5</v>
       </c>
-      <c r="L2" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2">
+      <c r="M2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N2">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>22</v>
+      <c r="O2" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:15">
       <c r="A3" s="3">
         <v>46231</v>
       </c>
       <c r="B3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F3">
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H3">
+        <v>1.441</v>
+      </c>
+      <c r="I3" s="1">
         <v>1.53</v>
       </c>
-      <c r="I3" s="1">
+      <c r="J3">
         <v>15.3</v>
       </c>
-      <c r="J3">
+      <c r="K3" s="1">
         <v>1.56</v>
       </c>
-      <c r="K3" s="1">
+      <c r="L3" s="1">
         <v>15.6</v>
       </c>
-      <c r="L3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M3">
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N3" t="s">
-        <v>23</v>
+      <c r="O3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:15">
       <c r="A6" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -666,29 +678,29 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:15">
       <c r="A7" s="5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:15">
       <c r="A8" s="6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B8" s="7">
         <v>35</v>
@@ -706,9 +718,9 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:15">
       <c r="A9" s="9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B9" s="10">
         <v>35</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -114,9 +111,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -210,10 +207,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +505,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -521,13 +518,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -570,107 +567,98 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>14</v>
-      </c>
     </row>
-    <row r="2" spans="1:15">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
         <v>46219</v>
       </c>
       <c r="B2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
         <v>17</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>19</v>
       </c>
       <c r="F2">
         <v>25</v>
       </c>
       <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2">
+        <v>1.47</v>
+      </c>
+      <c r="I2" s="1">
+        <v>36.75</v>
+      </c>
+      <c r="J2">
+        <v>1.5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>37.5</v>
+      </c>
+      <c r="L2" t="s">
         <v>20</v>
       </c>
-      <c r="H2">
-        <v>1.369</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.47</v>
-      </c>
-      <c r="J2">
-        <v>36.75</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="L2" s="1">
-        <v>37.5</v>
-      </c>
-      <c r="M2" t="s">
-        <v>21</v>
-      </c>
-      <c r="N2">
+      <c r="M2">
         <v>0</v>
       </c>
-      <c r="O2" t="s">
-        <v>23</v>
+      <c r="N2" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:15">
+    <row r="3" spans="1:14">
       <c r="A3" s="3">
         <v>46231</v>
       </c>
       <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
         <v>16</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>17</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>18</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
       </c>
       <c r="F3">
         <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H3">
-        <v>1.441</v>
+        <v>1.53</v>
       </c>
       <c r="I3" s="1">
-        <v>1.53</v>
+        <v>15.3</v>
       </c>
       <c r="J3">
-        <v>15.3</v>
+        <v>1.56</v>
       </c>
       <c r="K3" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L3" s="1">
         <v>15.6</v>
       </c>
-      <c r="M3" t="s">
-        <v>22</v>
-      </c>
-      <c r="N3">
+      <c r="L3" t="s">
+        <v>21</v>
+      </c>
+      <c r="M3">
         <v>0</v>
       </c>
-      <c r="O3" t="s">
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
         <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
-      <c r="A6" s="4" t="s">
-        <v>25</v>
       </c>
       <c r="B6" s="4"/>
       <c r="C6" s="4"/>
@@ -678,49 +666,49 @@
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
     </row>
-    <row r="7" spans="1:15">
+    <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="C7" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="D7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="5" t="s">
-        <v>29</v>
-      </c>
       <c r="E7" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:15">
+    <row r="8" spans="1:14">
       <c r="A8" s="6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="7">
         <v>35</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="8">
         <v>2</v>
       </c>
       <c r="D8" s="8">
-        <v>1.487143</v>
-      </c>
-      <c r="E8" s="7">
+        <v>1.487</v>
+      </c>
+      <c r="E8" s="8">
         <v>52.05</v>
       </c>
-      <c r="F8" s="7">
+      <c r="F8" s="8">
         <v>53.1</v>
       </c>
     </row>
-    <row r="9" spans="1:15">
+    <row r="9" spans="1:14">
       <c r="A9" s="9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B9" s="10">
         <v>35</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,9 +34,6 @@
     <t>Литри</t>
   </si>
   <si>
-    <t>Тип количество</t>
-  </si>
-  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -58,34 +55,40 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>1148 Варна пристанище</t>
-  </si>
-  <si>
-    <t>1158 Варна Чайка</t>
+    <t>Варна Порт</t>
+  </si>
+  <si>
+    <t>Варна Цар Освободител</t>
+  </si>
+  <si>
+    <t>Варна Чайка</t>
   </si>
   <si>
     <t>В6513КС</t>
   </si>
   <si>
+    <t>В7225ВР</t>
+  </si>
+  <si>
     <t>78970155027720238</t>
   </si>
   <si>
+    <t>78970155027720246</t>
+  </si>
+  <si>
     <t>95 EKONOMY UNLEADED</t>
   </si>
   <si>
-    <t>L15</t>
-  </si>
-  <si>
-    <t>15:14:00</t>
-  </si>
-  <si>
-    <t>11:16:00</t>
-  </si>
-  <si>
-    <t>3234894482 3234894482</t>
-  </si>
-  <si>
-    <t>3235484095 3235484095</t>
+    <t>E GAS LPG</t>
+  </si>
+  <si>
+    <t>13:16</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>11:17</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -111,9 +114,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -207,10 +210,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -505,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -514,17 +517,16 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="16.7109375" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" customWidth="1"/>
+    <col min="13" max="13" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -564,169 +566,221 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="3">
+        <v>46237</v>
+      </c>
+      <c r="B2" t="s">
         <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="3">
-        <v>46219</v>
-      </c>
-      <c r="B2" t="s">
-        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2">
+        <v>20</v>
+      </c>
+      <c r="G2" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H2">
+        <v>30.4</v>
+      </c>
+      <c r="I2" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J2">
+        <v>31</v>
+      </c>
+      <c r="K2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>241692</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="3">
+        <v>46244</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2">
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3">
+        <v>6.452</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="H3">
+        <v>9.807</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="J3">
+        <v>10.001</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3">
+        <v>435300</v>
+      </c>
+      <c r="M3">
+        <v>291418</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="3">
+        <v>46245</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4">
+        <v>20</v>
+      </c>
+      <c r="G4" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="H4">
+        <v>13</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="J4">
+        <v>13.2</v>
+      </c>
+      <c r="K4" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4">
+        <v>43570</v>
+      </c>
+      <c r="M4">
+        <v>145606</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G2" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2">
-        <v>1.47</v>
-      </c>
-      <c r="I2" s="1">
-        <v>36.75</v>
-      </c>
-      <c r="J2">
-        <v>1.5</v>
-      </c>
-      <c r="K2" s="1">
-        <v>37.5</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="3">
-        <v>46231</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" t="s">
-        <v>18</v>
-      </c>
-      <c r="F3">
-        <v>10</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3">
-        <v>1.53</v>
-      </c>
-      <c r="I3" s="1">
-        <v>15.3</v>
-      </c>
-      <c r="J3">
-        <v>1.56</v>
-      </c>
-      <c r="K3" s="1">
-        <v>15.6</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="B9" s="7">
+        <v>26.452</v>
+      </c>
+      <c r="C9" s="7">
+        <v>2</v>
+      </c>
+      <c r="D9" s="8">
+        <v>1.52</v>
+      </c>
+      <c r="E9" s="7">
+        <v>40.21</v>
+      </c>
+      <c r="F9" s="7">
+        <v>41.001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="7">
-        <v>35</v>
-      </c>
-      <c r="C8" s="8">
-        <v>2</v>
-      </c>
-      <c r="D8" s="8">
-        <v>1.487</v>
-      </c>
-      <c r="E8" s="8">
-        <v>52.05</v>
-      </c>
-      <c r="F8" s="8">
-        <v>53.1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="B9" s="10">
-        <v>35</v>
-      </c>
-      <c r="C9" s="10">
-        <v>2</v>
-      </c>
-      <c r="D9" s="8"/>
-      <c r="E9" s="10">
-        <v>52.05</v>
-      </c>
-      <c r="F9" s="10">
-        <v>53.1</v>
+      <c r="B10" s="7">
+        <v>20</v>
+      </c>
+      <c r="C10" s="7">
+        <v>1</v>
+      </c>
+      <c r="D10" s="8">
+        <v>0.65</v>
+      </c>
+      <c r="E10" s="7">
+        <v>13</v>
+      </c>
+      <c r="F10" s="7">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="10">
+        <v>46.452</v>
+      </c>
+      <c r="C11" s="10">
+        <v>3</v>
+      </c>
+      <c r="D11" s="8"/>
+      <c r="E11" s="10">
+        <v>53.21</v>
+      </c>
+      <c r="F11" s="10">
+        <v>54.201</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="31">
   <si>
     <t>Дата</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Литри</t>
   </si>
   <si>
+    <t>Тип количество</t>
+  </si>
+  <si>
     <t>GTA цена</t>
   </si>
   <si>
@@ -55,24 +58,15 @@
     <t>Billing_Document</t>
   </si>
   <si>
-    <t>Варна Порт</t>
-  </si>
-  <si>
-    <t>Варна Цар Освободител</t>
-  </si>
-  <si>
-    <t>Варна Чайка</t>
-  </si>
-  <si>
-    <t>В6513КС</t>
+    <t>1199 Varna Car Osvoboditel</t>
+  </si>
+  <si>
+    <t>1148 Варна пристанище</t>
   </si>
   <si>
     <t>В7225ВР</t>
   </si>
   <si>
-    <t>78970155027720238</t>
-  </si>
-  <si>
     <t>78970155027720246</t>
   </si>
   <si>
@@ -82,13 +76,19 @@
     <t>E GAS LPG</t>
   </si>
   <si>
-    <t>13:16</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>11:17</t>
+    <t>L15</t>
+  </si>
+  <si>
+    <t>15:09:00</t>
+  </si>
+  <si>
+    <t>10:29:00</t>
+  </si>
+  <si>
+    <t>3236576070 3236576070</t>
+  </si>
+  <si>
+    <t>3236721726 3236721726</t>
   </si>
   <si>
     <t>Общи литри по продукт / ОП ИНВЕСТИЦИОННА ПОЛИТИКА</t>
@@ -113,10 +113,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
+  <numFmts count="4">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="#,##0.00000"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="#,##0.00000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -196,7 +197,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -210,10 +211,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -508,7 +511,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -517,16 +520,17 @@
     <col min="4" max="4" width="28.7109375" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" customWidth="1"/>
     <col min="6" max="6" width="18.7109375" customWidth="1"/>
-    <col min="7" max="7" width="15.7109375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" customWidth="1"/>
-    <col min="13" max="13" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -566,221 +570,189 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:14">
       <c r="A2" s="3">
-        <v>46237</v>
+        <v>46252</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
         <v>16</v>
       </c>
       <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2">
+        <v>3.5</v>
+      </c>
+      <c r="G2" t="s">
         <v>20</v>
       </c>
-      <c r="F2">
+      <c r="H2" s="1">
+        <v>1.429</v>
+      </c>
+      <c r="I2" s="1">
+        <v>5.002</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="K2" s="1">
+        <v>5.46</v>
+      </c>
+      <c r="L2" t="s">
+        <v>21</v>
+      </c>
+      <c r="M2">
+        <v>43730</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="3">
+        <v>46255</v>
+      </c>
+      <c r="B3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3">
         <v>20</v>
       </c>
-      <c r="G2" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H2">
-        <v>30.4</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J2">
-        <v>31</v>
-      </c>
-      <c r="K2" t="s">
+      <c r="G3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.99</v>
+      </c>
+      <c r="I3" s="1">
+        <v>19.8</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0.66</v>
+      </c>
+      <c r="K3" s="1">
+        <v>13.2</v>
+      </c>
+      <c r="L3" t="s">
         <v>22</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>241692</v>
+      <c r="M3">
+        <v>43800</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="3">
-        <v>46244</v>
-      </c>
-      <c r="B3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" t="s">
+    <row r="6" spans="1:14">
+      <c r="A6" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="E3" t="s">
+      <c r="B8" s="7">
         <v>20</v>
       </c>
-      <c r="F3">
-        <v>6.452</v>
-      </c>
-      <c r="G3" s="1">
-        <v>1.52</v>
-      </c>
-      <c r="H3">
-        <v>9.807</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="J3">
-        <v>10.001</v>
-      </c>
-      <c r="K3" t="s">
-        <v>23</v>
-      </c>
-      <c r="L3">
-        <v>435300</v>
-      </c>
-      <c r="M3">
-        <v>291418</v>
+      <c r="C8" s="8">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0.99</v>
+      </c>
+      <c r="E8" s="7">
+        <v>19.8</v>
+      </c>
+      <c r="F8" s="7">
+        <v>13.2</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="3">
-        <v>46245</v>
-      </c>
-      <c r="B4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4">
-        <v>20</v>
-      </c>
-      <c r="G4" s="1">
-        <v>0.65</v>
-      </c>
-      <c r="H4">
-        <v>13</v>
-      </c>
-      <c r="I4" s="1">
-        <v>0.66</v>
-      </c>
-      <c r="J4">
-        <v>13.2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>24</v>
-      </c>
-      <c r="L4">
-        <v>43570</v>
-      </c>
-      <c r="M4">
-        <v>145606</v>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7">
+        <v>3.5</v>
+      </c>
+      <c r="C9" s="8">
+        <v>1</v>
+      </c>
+      <c r="D9" s="9">
+        <v>1.42914</v>
+      </c>
+      <c r="E9" s="7">
+        <v>5</v>
+      </c>
+      <c r="F9" s="7">
+        <v>5.46</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="7">
-        <v>26.452</v>
-      </c>
-      <c r="C9" s="7">
+    <row r="10" spans="1:14">
+      <c r="A10" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="11">
+        <v>23.5</v>
+      </c>
+      <c r="C10" s="12">
         <v>2</v>
       </c>
-      <c r="D9" s="8">
-        <v>1.52</v>
-      </c>
-      <c r="E9" s="7">
-        <v>40.21</v>
-      </c>
-      <c r="F9" s="7">
-        <v>41.001</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="B10" s="7">
-        <v>20</v>
-      </c>
-      <c r="C10" s="7">
-        <v>1</v>
-      </c>
-      <c r="D10" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="E10" s="7">
-        <v>13</v>
-      </c>
-      <c r="F10" s="7">
-        <v>13.2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="B11" s="10">
-        <v>46.452</v>
-      </c>
-      <c r="C11" s="10">
-        <v>3</v>
-      </c>
-      <c r="D11" s="8"/>
-      <c r="E11" s="10">
-        <v>53.21</v>
-      </c>
-      <c r="F11" s="10">
-        <v>54.201</v>
+      <c r="D10" s="9"/>
+      <c r="E10" s="11">
+        <v>24.8</v>
+      </c>
+      <c r="F10" s="11">
+        <v>18.66</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A6:F6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ОП ИНВЕСТИЦИОННА ПОЛИТИКА/ОП ИНВЕСТИЦИОННА ПОЛИТИКА.xlsx
@@ -597,10 +597,10 @@
         <v>20</v>
       </c>
       <c r="H2" s="1">
-        <v>1.429</v>
+        <v>1.53</v>
       </c>
       <c r="I2" s="1">
-        <v>5.002</v>
+        <v>5.355</v>
       </c>
       <c r="J2" s="1">
         <v>1.56</v>
@@ -641,10 +641,10 @@
         <v>20</v>
       </c>
       <c r="H3" s="1">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="I3" s="1">
-        <v>19.8</v>
+        <v>13</v>
       </c>
       <c r="J3" s="1">
         <v>0.66</v>
@@ -703,10 +703,10 @@
         <v>1</v>
       </c>
       <c r="D8" s="9">
-        <v>0.99</v>
+        <v>0.65</v>
       </c>
       <c r="E8" s="7">
-        <v>19.8</v>
+        <v>13</v>
       </c>
       <c r="F8" s="7">
         <v>13.2</v>
@@ -723,10 +723,10 @@
         <v>1</v>
       </c>
       <c r="D9" s="9">
-        <v>1.42914</v>
+        <v>1.53</v>
       </c>
       <c r="E9" s="7">
-        <v>5</v>
+        <v>5.36</v>
       </c>
       <c r="F9" s="7">
         <v>5.46</v>
@@ -744,7 +744,7 @@
       </c>
       <c r="D10" s="9"/>
       <c r="E10" s="11">
-        <v>24.8</v>
+        <v>18.36</v>
       </c>
       <c r="F10" s="11">
         <v>18.66</v>
